--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T16:33:35+00:00</t>
+    <t>2025-04-24T12:56:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1292,17 +1292,17 @@
   <dimension ref="A1:AN81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="58.4765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.0078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.8984375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="21.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="50.1328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.44140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="17.05859375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="119.41015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="102.375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1311,26 +1311,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="168.19140625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="49.01171875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.98046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="144.1953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="42.01953125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.98828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="28.1484375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="50.08203125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="42.9765625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="42.9375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:56:51+00:00</t>
+    <t>2025-04-24T12:57:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:57:11+00:00</t>
+    <t>2025-04-24T13:09:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T13:09:23+00:00</t>
+    <t>2025-04-29T14:26:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T14:28:01+00:00</t>
+    <t>2026-03-04T14:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T14:06:01+00:00</t>
+    <t>2026-03-04T14:38:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T14:38:02+00:00</t>
+    <t>2026-03-04T16:46:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2929" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2929" uniqueCount="310">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T16:46:41+00:00</t>
+    <t>2026-05-06T07:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -884,10 +884,6 @@
   </si>
   <si>
     <t>Usually, this is used for documents other than those defined by FHIR.</t>
-  </si>
-  <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}iti-mhd-repl:a DocumetReference replacements needs to relate to a superseded DocumentReference {relatesTo.empty() or (relatesTo.code='replaces' implies relatesTo.target.exists())}</t>
   </si>
   <si>
     <t>Document[classCode="DOC" and moodCode="EVN"]</t>
@@ -7358,7 +7354,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>87</v>
@@ -7558,16 +7554,16 @@
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AK55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -7575,7 +7571,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>195</v>
@@ -7687,7 +7683,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>199</v>
@@ -7799,7 +7795,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>200</v>
@@ -7913,7 +7909,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>201</v>
@@ -8029,7 +8025,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>202</v>
@@ -8143,7 +8139,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>208</v>
@@ -8257,7 +8253,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>213</v>
@@ -8369,7 +8365,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>217</v>
@@ -8481,7 +8477,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>218</v>
@@ -8595,7 +8591,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>219</v>
@@ -8711,7 +8707,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>220</v>
@@ -8823,7 +8819,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>225</v>
@@ -8937,7 +8933,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>229</v>
@@ -9049,7 +9045,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>232</v>
@@ -9161,7 +9157,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>234</v>
@@ -9273,7 +9269,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>237</v>
@@ -9385,7 +9381,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>240</v>
@@ -9497,7 +9493,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>244</v>
@@ -9609,7 +9605,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>245</v>
@@ -9723,7 +9719,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>246</v>
@@ -9839,7 +9835,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>247</v>
@@ -9951,7 +9947,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>250</v>
@@ -10063,7 +10059,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>253</v>
@@ -10177,7 +10173,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>257</v>
@@ -10291,7 +10287,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>261</v>
@@ -10405,10 +10401,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10431,19 +10427,19 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -10492,7 +10488,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:19:11+00:00</t>
+    <t>2026-05-27T14:14:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:14:06+00:00</t>
+    <t>2026-05-28T14:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:04:20+00:00</t>
+    <t>2026-05-28T14:30:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:30:01+00:00</t>
+    <t>2026-06-03T13:49:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T13:49:29+00:00</t>
+    <t>2026-06-03T13:50:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T13:50:50+00:00</t>
+    <t>2026-06-30T13:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:26:19+00:00</t>
+    <t>2026-06-30T13:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:34:41+00:00</t>
+    <t>2026-06-30T16:19:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T16:19:40+00:00</t>
+    <t>2026-07-15T16:15:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:15:50+00:00</t>
+    <t>2026-07-27T15:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:55:54+00:00</t>
+    <t>2026-08-06T13:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:06:39+00:00</t>
+    <t>2026-08-06T14:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
+++ b/main/ig/StructureDefinition-pdsm-find-documentreferences-comprehensive-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:18:59+00:00</t>
+    <t>2026-08-06T14:57:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
